--- a/backend/data/financials_by_company/1991.HK.xlsx
+++ b/backend/data/financials_by_company/1991.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,199 +662,109 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-3511500</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18785000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-14046000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-14046000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-63632000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28783000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>853474000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4739000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-24044000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-20264000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>28281000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8017000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-53097500</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-63632000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>990414000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>130717000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>130717000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.487</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.487</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-63632000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-63632000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-63632000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-10493000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-53139000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-53139000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>814000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-52325000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1787000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-13551000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-9428000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23296000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-317000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-20264000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28281000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>8017000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-20353000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>136940000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>144995000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>24384000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>120611000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>116587000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>853474000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>970061000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>970061000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>6472000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>5633250</v>
+        <v>-3793250</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-46949000</v>
+        <v>-22087000</v>
       </c>
       <c r="E3" t="n">
-        <v>22533000</v>
+        <v>-15173000</v>
       </c>
       <c r="F3" t="n">
-        <v>22533000</v>
+        <v>-15173000</v>
       </c>
       <c r="G3" t="n">
-        <v>-88035000</v>
+        <v>-98063000</v>
       </c>
       <c r="H3" t="n">
-        <v>29636000</v>
+        <v>31562000</v>
       </c>
       <c r="I3" t="n">
-        <v>1120813000</v>
+        <v>260061000</v>
       </c>
       <c r="J3" t="n">
-        <v>-24416000</v>
+        <v>-37260000</v>
       </c>
       <c r="K3" t="n">
-        <v>-54052000</v>
+        <v>-68822000</v>
       </c>
       <c r="L3" t="n">
-        <v>-24357000</v>
+        <v>-22543000</v>
       </c>
       <c r="M3" t="n">
-        <v>30549000</v>
+        <v>27989000</v>
       </c>
       <c r="N3" t="n">
-        <v>6192000</v>
+        <v>5446000</v>
       </c>
       <c r="O3" t="n">
-        <v>-104934750</v>
+        <v>-86683250</v>
       </c>
       <c r="P3" t="n">
-        <v>-88035000</v>
+        <v>-98063000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1304975000</v>
+        <v>421403000</v>
       </c>
       <c r="R3" t="n">
         <v>130676700</v>
@@ -863,144 +773,142 @@
         <v>130676700</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.674</v>
+        <v>-0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.674</v>
+        <v>-0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>-88035000</v>
+        <v>-98063000</v>
       </c>
       <c r="W3" t="n">
-        <v>-88035000</v>
+        <v>-98063000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-88035000</v>
+        <v>-98063000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2326000</v>
+        <v>841000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-85709000</v>
+        <v>-98904000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-85709000</v>
+        <v>-98904000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1108000</v>
+        <v>2093000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-84601000</v>
+        <v>-96811000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3682000</v>
+        <v>3916000</v>
       </c>
       <c r="AF3" t="n">
-        <v>22533000</v>
+        <v>-15149000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-26880000</v>
+        <v>-5659000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4347000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
+        <v>20808000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-24357000</v>
+        <v>-22543000</v>
       </c>
       <c r="AK3" t="n">
-        <v>30549000</v>
+        <v>27989000</v>
       </c>
       <c r="AL3" t="n">
-        <v>6192000</v>
+        <v>5446000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-91145000</v>
+        <v>-77862000</v>
       </c>
       <c r="AN3" t="n">
-        <v>184162000</v>
+        <v>161342000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8000</v>
+        <v>124000</v>
       </c>
       <c r="AP3" t="n">
-        <v>185126000</v>
+        <v>161955000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>35839000</v>
+        <v>23078000</v>
       </c>
       <c r="AR3" t="n">
-        <v>149287000</v>
+        <v>138877000</v>
       </c>
       <c r="AS3" t="n">
-        <v>93017000</v>
+        <v>83480000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1120813000</v>
+        <v>260061000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1213830000</v>
+        <v>343541000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1213830000</v>
+        <v>343541000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3793250</v>
+        <v>5633250</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-22087000</v>
+        <v>-46949000</v>
       </c>
       <c r="E4" t="n">
-        <v>-15173000</v>
+        <v>22533000</v>
       </c>
       <c r="F4" t="n">
-        <v>-15173000</v>
+        <v>22533000</v>
       </c>
       <c r="G4" t="n">
-        <v>-98063000</v>
+        <v>-88035000</v>
       </c>
       <c r="H4" t="n">
-        <v>31562000</v>
+        <v>29636000</v>
       </c>
       <c r="I4" t="n">
-        <v>260061000</v>
+        <v>1120813000</v>
       </c>
       <c r="J4" t="n">
-        <v>-37260000</v>
+        <v>-24416000</v>
       </c>
       <c r="K4" t="n">
-        <v>-68822000</v>
+        <v>-54052000</v>
       </c>
       <c r="L4" t="n">
-        <v>-22543000</v>
+        <v>-24357000</v>
       </c>
       <c r="M4" t="n">
-        <v>27989000</v>
+        <v>30549000</v>
       </c>
       <c r="N4" t="n">
-        <v>5446000</v>
+        <v>6192000</v>
       </c>
       <c r="O4" t="n">
-        <v>-86683250</v>
+        <v>-104934750</v>
       </c>
       <c r="P4" t="n">
-        <v>-98063000</v>
+        <v>-88035000</v>
       </c>
       <c r="Q4" t="n">
-        <v>421403000</v>
+        <v>1304975000</v>
       </c>
       <c r="R4" t="n">
         <v>130676700</v>
@@ -1009,233 +917,379 @@
         <v>130676700</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.75</v>
+        <v>-0.674</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.75</v>
+        <v>-0.674</v>
       </c>
       <c r="V4" t="n">
-        <v>-98063000</v>
+        <v>-88035000</v>
       </c>
       <c r="W4" t="n">
-        <v>-98063000</v>
+        <v>-88035000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-98063000</v>
+        <v>-88035000</v>
       </c>
       <c r="Z4" t="n">
-        <v>841000</v>
+        <v>-2326000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-98904000</v>
+        <v>-85709000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-98904000</v>
+        <v>-85709000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2093000</v>
+        <v>1108000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-96811000</v>
+        <v>-84601000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3916000</v>
+        <v>3682000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-15149000</v>
+        <v>22533000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5659000</v>
+        <v>-26880000</v>
       </c>
       <c r="AH4" t="n">
-        <v>20808000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>4347000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-22543000</v>
+        <v>-24357000</v>
       </c>
       <c r="AK4" t="n">
-        <v>27989000</v>
+        <v>30549000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5446000</v>
+        <v>6192000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-77862000</v>
+        <v>-91145000</v>
       </c>
       <c r="AN4" t="n">
-        <v>161342000</v>
+        <v>184162000</v>
       </c>
       <c r="AO4" t="n">
-        <v>124000</v>
+        <v>8000</v>
       </c>
       <c r="AP4" t="n">
-        <v>161955000</v>
+        <v>185126000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23078000</v>
+        <v>35839000</v>
       </c>
       <c r="AR4" t="n">
-        <v>138877000</v>
+        <v>149287000</v>
       </c>
       <c r="AS4" t="n">
-        <v>83480000</v>
+        <v>93017000</v>
       </c>
       <c r="AT4" t="n">
-        <v>260061000</v>
+        <v>1120813000</v>
       </c>
       <c r="AU4" t="n">
-        <v>343541000</v>
+        <v>1213830000</v>
       </c>
       <c r="AV4" t="n">
-        <v>343541000</v>
+        <v>1213830000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-899691.787096</v>
+        <v>-3511500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.075706</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-25556000</v>
+        <v>18785000</v>
       </c>
       <c r="E5" t="n">
-        <v>-11884000</v>
+        <v>-14046000</v>
       </c>
       <c r="F5" t="n">
-        <v>-11884000</v>
+        <v>-14046000</v>
       </c>
       <c r="G5" t="n">
-        <v>-84901000</v>
+        <v>-63632000</v>
       </c>
       <c r="H5" t="n">
-        <v>32537000</v>
+        <v>28783000</v>
       </c>
       <c r="I5" t="n">
-        <v>286247000</v>
+        <v>853474000</v>
       </c>
       <c r="J5" t="n">
-        <v>-37440000</v>
+        <v>4739000</v>
       </c>
       <c r="K5" t="n">
-        <v>-69977000</v>
+        <v>-24044000</v>
       </c>
       <c r="L5" t="n">
-        <v>-17089000</v>
+        <v>-20264000</v>
       </c>
       <c r="M5" t="n">
-        <v>22816000</v>
+        <v>28281000</v>
       </c>
       <c r="N5" t="n">
-        <v>5727000</v>
+        <v>8017000</v>
       </c>
       <c r="O5" t="n">
-        <v>-73916691.78709599</v>
+        <v>-53097500</v>
       </c>
       <c r="P5" t="n">
-        <v>-84901000</v>
+        <v>-63632000</v>
       </c>
       <c r="Q5" t="n">
-        <v>465213000</v>
+        <v>990414000</v>
       </c>
       <c r="R5" t="n">
-        <v>112929500</v>
+        <v>130717000</v>
       </c>
       <c r="S5" t="n">
-        <v>112929500</v>
+        <v>130717000</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.752</v>
+        <v>-0.4868</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.752</v>
+        <v>-0.4868</v>
       </c>
       <c r="V5" t="n">
-        <v>-84901000</v>
+        <v>-63632000</v>
       </c>
       <c r="W5" t="n">
-        <v>-84901000</v>
+        <v>-63632000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-84901000</v>
+        <v>-63632000</v>
       </c>
       <c r="Z5" t="n">
-        <v>867000</v>
+        <v>-10493000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-85768000</v>
+        <v>-53139000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-85768000</v>
+        <v>-53139000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7025000</v>
+        <v>814000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-92793000</v>
+        <v>-52325000</v>
       </c>
       <c r="AE5" t="n">
-        <v>10436000</v>
+        <v>1787000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-11884000</v>
+        <v>-13551000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-11642000</v>
+        <v>-9428000</v>
       </c>
       <c r="AH5" t="n">
-        <v>23526000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>23296000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-317000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-17089000</v>
+        <v>-20264000</v>
       </c>
       <c r="AK5" t="n">
-        <v>22816000</v>
+        <v>28281000</v>
       </c>
       <c r="AL5" t="n">
-        <v>5727000</v>
+        <v>8017000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-102685000</v>
+        <v>-20353000</v>
       </c>
       <c r="AN5" t="n">
-        <v>178966000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>6472000</v>
-      </c>
+        <v>136940000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>179148000</v>
+        <v>144995000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22125000</v>
+        <v>24384000</v>
       </c>
       <c r="AR5" t="n">
-        <v>157023000</v>
+        <v>120611000</v>
       </c>
       <c r="AS5" t="n">
-        <v>76281000</v>
+        <v>116587000</v>
       </c>
       <c r="AT5" t="n">
-        <v>286247000</v>
+        <v>853474000</v>
       </c>
       <c r="AU5" t="n">
-        <v>362528000</v>
+        <v>970061000</v>
       </c>
       <c r="AV5" t="n">
-        <v>362528000</v>
+        <v>970061000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-4722500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-9577000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-18890000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-18890000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16416000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>669700000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-28467000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-44883000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-21513000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>27648000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6135000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-59177500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>792477000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>147591000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>147591000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.4969</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.4969</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-72676000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-72676000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>145000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-72531000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1739000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-18890000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1499000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>20389000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-21513000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27648000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6135000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-34324000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>122777000</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>124276000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12739000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>111537000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>88453000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>669700000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>758153000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>758153000</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,226 +1672,102 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>131346700</v>
-      </c>
-      <c r="C2" t="n">
-        <v>131346700</v>
-      </c>
-      <c r="D2" t="n">
-        <v>205407000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>240162000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10796000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>248679000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-135013000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10796000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22831000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>31348000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>84287000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>30399000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-949000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>31348000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6537000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6739000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1065203000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>763800000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>131347000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>131347000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>585622000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>65179000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1601000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1959000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>61619000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>8680000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>52939000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>520443000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>178543000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>14151000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>164392000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>228298000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>156855000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>16761000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>54682000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>616021000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>230591000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>16268000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>11203000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>11203000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>20552000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>20552000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>111602000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-218240000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>329842000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>24400000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>37324000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>185415000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>60766000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>46337000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>385430000</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
+        <v>820000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="n">
+        <v>205053000</v>
+      </c>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>168948000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>30673000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>22015000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3971000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4687000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>120266000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>53619000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-5991000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>59610000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>11924000</v>
-      </c>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="n">
-        <v>11924000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>11924000</v>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>130676700</v>
@@ -1846,49 +1776,47 @@
         <v>130676700</v>
       </c>
       <c r="D3" t="n">
-        <v>188591000</v>
+        <v>172304000</v>
       </c>
       <c r="E3" t="n">
-        <v>266075000</v>
+        <v>261263000</v>
       </c>
       <c r="F3" t="n">
-        <v>51714000</v>
+        <v>135297000</v>
       </c>
       <c r="G3" t="n">
-        <v>268351000</v>
+        <v>333772000</v>
       </c>
       <c r="H3" t="n">
-        <v>-133596000</v>
+        <v>-133810000</v>
       </c>
       <c r="I3" t="n">
-        <v>51714000</v>
+        <v>135297000</v>
       </c>
       <c r="J3" t="n">
-        <v>72156000</v>
+        <v>64954000</v>
       </c>
       <c r="K3" t="n">
-        <v>74432000</v>
+        <v>137463000</v>
       </c>
       <c r="L3" t="n">
-        <v>120000000</v>
+        <v>141596000</v>
       </c>
       <c r="M3" t="n">
-        <v>67576000</v>
+        <v>136380000</v>
       </c>
       <c r="N3" t="n">
-        <v>-6856000</v>
+        <v>-1083000</v>
       </c>
       <c r="O3" t="n">
-        <v>74432000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6537000</v>
-      </c>
+        <v>137463000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>6739000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1001571000</v>
+        <v>-913536000</v>
       </c>
       <c r="S3" t="n">
         <v>763800000</v>
@@ -1900,162 +1828,163 @@
         <v>130677000</v>
       </c>
       <c r="V3" t="n">
-        <v>631610000</v>
+        <v>505137000</v>
       </c>
       <c r="W3" t="n">
-        <v>104977000</v>
+        <v>60917000</v>
       </c>
       <c r="X3" t="n">
-        <v>1760000</v>
+        <v>1890000</v>
       </c>
       <c r="Y3" t="n">
         <v>2784000</v>
       </c>
       <c r="Z3" t="n">
-        <v>100433000</v>
+        <v>56243000</v>
       </c>
       <c r="AA3" t="n">
-        <v>54865000</v>
+        <v>52110000</v>
       </c>
       <c r="AB3" t="n">
-        <v>45568000</v>
+        <v>4133000</v>
       </c>
       <c r="AC3" t="n">
-        <v>526633000</v>
+        <v>444220000</v>
       </c>
       <c r="AD3" t="n">
-        <v>165642000</v>
+        <v>205020000</v>
       </c>
       <c r="AE3" t="n">
-        <v>17291000</v>
+        <v>12844000</v>
       </c>
       <c r="AF3" t="n">
-        <v>148351000</v>
+        <v>192176000</v>
       </c>
       <c r="AG3" t="n">
-        <v>245276000</v>
+        <v>207687000</v>
       </c>
       <c r="AH3" t="n">
-        <v>165843000</v>
+        <v>115207000</v>
       </c>
       <c r="AI3" t="n">
-        <v>17466000</v>
+        <v>25361000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>61967000</v>
+        <v>67119000</v>
       </c>
       <c r="AK3" t="n">
-        <v>699186000</v>
+        <v>641517000</v>
       </c>
       <c r="AL3" t="n">
-        <v>306149000</v>
+        <v>331107000</v>
       </c>
       <c r="AM3" t="n">
-        <v>15927000</v>
+        <v>16658000</v>
       </c>
       <c r="AN3" t="n">
-        <v>441000</v>
+        <v>448000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3452000</v>
+        <v>3183000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2957000</v>
+        <v>3183000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>495000</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4812000</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4812000</v>
       </c>
       <c r="AT3" t="n">
         <v>21000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>22718000</v>
+        <v>2166000</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>22718000</v>
+        <v>2166000</v>
       </c>
       <c r="AX3" t="n">
-        <v>190176000</v>
+        <v>236551000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-230513000</v>
+        <v>-223809000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>420689000</v>
+        <v>460360000</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>445000</v>
       </c>
       <c r="BB3" t="n">
-        <v>46691000</v>
+        <v>62144000</v>
       </c>
       <c r="BC3" t="n">
-        <v>205485000</v>
+        <v>209938000</v>
       </c>
       <c r="BD3" t="n">
-        <v>110014000</v>
+        <v>103600000</v>
       </c>
       <c r="BE3" t="n">
-        <v>58499000</v>
+        <v>84233000</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>393037000</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="n">
-        <v>22696000</v>
-      </c>
+        <v>310410000</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>154558000</v>
+        <v>35952000</v>
       </c>
       <c r="BK3" t="n">
-        <v>38074000</v>
+        <v>59221000</v>
       </c>
       <c r="BL3" t="n">
-        <v>29087000</v>
+        <v>47791000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3825000</v>
+        <v>3019000</v>
       </c>
       <c r="BN3" t="n">
-        <v>5162000</v>
+        <v>8411000</v>
       </c>
       <c r="BO3" t="n">
-        <v>116074000</v>
+        <v>127636000</v>
       </c>
       <c r="BP3" t="n">
-        <v>56307000</v>
+        <v>63596000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-5747000</v>
+        <v>-7718000</v>
       </c>
       <c r="BR3" t="n">
-        <v>62054000</v>
+        <v>71314000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5328000</v>
+        <v>24005000</v>
       </c>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="n">
-        <v>5328000</v>
+        <v>24005000</v>
       </c>
       <c r="BV3" t="n">
-        <v>5328000</v>
-      </c>
+        <v>24005000</v>
+      </c>
+      <c r="BW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>130676700</v>
@@ -2064,47 +1993,49 @@
         <v>130676700</v>
       </c>
       <c r="D4" t="n">
-        <v>172304000</v>
+        <v>188591000</v>
       </c>
       <c r="E4" t="n">
-        <v>261263000</v>
+        <v>266075000</v>
       </c>
       <c r="F4" t="n">
-        <v>135297000</v>
+        <v>51714000</v>
       </c>
       <c r="G4" t="n">
-        <v>333772000</v>
+        <v>268351000</v>
       </c>
       <c r="H4" t="n">
-        <v>-133810000</v>
+        <v>-133596000</v>
       </c>
       <c r="I4" t="n">
-        <v>135297000</v>
+        <v>51714000</v>
       </c>
       <c r="J4" t="n">
-        <v>64954000</v>
+        <v>72156000</v>
       </c>
       <c r="K4" t="n">
-        <v>137463000</v>
+        <v>74432000</v>
       </c>
       <c r="L4" t="n">
-        <v>141596000</v>
+        <v>120000000</v>
       </c>
       <c r="M4" t="n">
-        <v>136380000</v>
+        <v>67576000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1083000</v>
+        <v>-6856000</v>
       </c>
       <c r="O4" t="n">
-        <v>137463000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>74432000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6537000</v>
+      </c>
       <c r="Q4" t="n">
         <v>6739000</v>
       </c>
       <c r="R4" t="n">
-        <v>-913536000</v>
+        <v>-1001571000</v>
       </c>
       <c r="S4" t="n">
         <v>763800000</v>
@@ -2116,367 +2047,590 @@
         <v>130677000</v>
       </c>
       <c r="V4" t="n">
-        <v>505137000</v>
+        <v>631610000</v>
       </c>
       <c r="W4" t="n">
-        <v>60917000</v>
+        <v>104977000</v>
       </c>
       <c r="X4" t="n">
-        <v>1890000</v>
+        <v>1760000</v>
       </c>
       <c r="Y4" t="n">
         <v>2784000</v>
       </c>
       <c r="Z4" t="n">
-        <v>56243000</v>
+        <v>100433000</v>
       </c>
       <c r="AA4" t="n">
-        <v>52110000</v>
+        <v>54865000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4133000</v>
+        <v>45568000</v>
       </c>
       <c r="AC4" t="n">
-        <v>444220000</v>
+        <v>526633000</v>
       </c>
       <c r="AD4" t="n">
-        <v>205020000</v>
+        <v>165642000</v>
       </c>
       <c r="AE4" t="n">
-        <v>12844000</v>
+        <v>17291000</v>
       </c>
       <c r="AF4" t="n">
-        <v>192176000</v>
+        <v>148351000</v>
       </c>
       <c r="AG4" t="n">
-        <v>207687000</v>
+        <v>245276000</v>
       </c>
       <c r="AH4" t="n">
-        <v>115207000</v>
+        <v>165843000</v>
       </c>
       <c r="AI4" t="n">
-        <v>25361000</v>
+        <v>17466000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67119000</v>
+        <v>61967000</v>
       </c>
       <c r="AK4" t="n">
-        <v>641517000</v>
+        <v>699186000</v>
       </c>
       <c r="AL4" t="n">
-        <v>331107000</v>
+        <v>306149000</v>
       </c>
       <c r="AM4" t="n">
-        <v>16658000</v>
+        <v>15927000</v>
       </c>
       <c r="AN4" t="n">
-        <v>448000</v>
+        <v>441000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3183000</v>
+        <v>3452000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3183000</v>
+        <v>2957000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>495000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4812000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>4812000</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
         <v>21000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2166000</v>
+        <v>22718000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>2166000</v>
+        <v>22718000</v>
       </c>
       <c r="AX4" t="n">
-        <v>236551000</v>
+        <v>190176000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-223809000</v>
+        <v>-230513000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>460360000</v>
+        <v>420689000</v>
       </c>
       <c r="BA4" t="n">
-        <v>445000</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>62144000</v>
+        <v>46691000</v>
       </c>
       <c r="BC4" t="n">
-        <v>209938000</v>
+        <v>205485000</v>
       </c>
       <c r="BD4" t="n">
-        <v>103600000</v>
+        <v>110014000</v>
       </c>
       <c r="BE4" t="n">
-        <v>84233000</v>
+        <v>58499000</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>310410000</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
+        <v>393037000</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="n">
+        <v>22696000</v>
+      </c>
       <c r="BJ4" t="n">
-        <v>35952000</v>
+        <v>154558000</v>
       </c>
       <c r="BK4" t="n">
-        <v>59221000</v>
+        <v>38074000</v>
       </c>
       <c r="BL4" t="n">
-        <v>47791000</v>
+        <v>29087000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3019000</v>
+        <v>3825000</v>
       </c>
       <c r="BN4" t="n">
-        <v>8411000</v>
+        <v>5162000</v>
       </c>
       <c r="BO4" t="n">
-        <v>127636000</v>
+        <v>116074000</v>
       </c>
       <c r="BP4" t="n">
-        <v>63596000</v>
+        <v>56307000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-7718000</v>
+        <v>-5747000</v>
       </c>
       <c r="BR4" t="n">
-        <v>71314000</v>
+        <v>62054000</v>
       </c>
       <c r="BS4" t="n">
-        <v>24005000</v>
+        <v>5328000</v>
       </c>
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="n">
-        <v>24005000</v>
+        <v>5328000</v>
       </c>
       <c r="BV4" t="n">
-        <v>24005000</v>
-      </c>
+        <v>5328000</v>
+      </c>
+      <c r="BW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>130676700</v>
+        <v>131346700</v>
       </c>
       <c r="C5" t="n">
-        <v>130676700</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>131346700</v>
+      </c>
+      <c r="D5" t="n">
+        <v>205407000</v>
+      </c>
       <c r="E5" t="n">
-        <v>78796000</v>
+        <v>240162000</v>
       </c>
       <c r="F5" t="n">
-        <v>240294000</v>
+        <v>10796000</v>
       </c>
       <c r="G5" t="n">
-        <v>258106000</v>
+        <v>248679000</v>
       </c>
       <c r="H5" t="n">
-        <v>114509000</v>
+        <v>-135013000</v>
       </c>
       <c r="I5" t="n">
-        <v>240294000</v>
+        <v>10796000</v>
       </c>
       <c r="J5" t="n">
-        <v>63150000</v>
+        <v>22831000</v>
       </c>
       <c r="K5" t="n">
-        <v>242460000</v>
+        <v>31348000</v>
       </c>
       <c r="L5" t="n">
-        <v>244606000</v>
+        <v>84287000</v>
       </c>
       <c r="M5" t="n">
-        <v>241938000</v>
+        <v>30399000</v>
       </c>
       <c r="N5" t="n">
-        <v>-522000</v>
+        <v>-949000</v>
       </c>
       <c r="O5" t="n">
-        <v>242460000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>31348000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6537000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6739000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1065203000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>763800000</v>
+      </c>
       <c r="T5" t="n">
-        <v>130677000</v>
+        <v>131347000</v>
       </c>
       <c r="U5" t="n">
-        <v>130677000</v>
+        <v>131347000</v>
       </c>
       <c r="V5" t="n">
-        <v>546511000</v>
+        <v>585622000</v>
       </c>
       <c r="W5" t="n">
-        <v>53492000</v>
+        <v>65179000</v>
       </c>
       <c r="X5" t="n">
-        <v>2281000</v>
+        <v>1601000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1959000</v>
       </c>
       <c r="Z5" t="n">
-        <v>51211000</v>
+        <v>61619000</v>
       </c>
       <c r="AA5" t="n">
-        <v>49065000</v>
+        <v>8680000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2146000</v>
+        <v>52939000</v>
       </c>
       <c r="AC5" t="n">
-        <v>493019000</v>
+        <v>520443000</v>
       </c>
       <c r="AD5" t="n">
-        <v>27585000</v>
+        <v>178543000</v>
       </c>
       <c r="AE5" t="n">
-        <v>14085000</v>
+        <v>14151000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13500000</v>
+        <v>164392000</v>
       </c>
       <c r="AG5" t="n">
-        <v>96725000</v>
+        <v>228298000</v>
       </c>
       <c r="AH5" t="n">
-        <v>10913000</v>
+        <v>156855000</v>
       </c>
       <c r="AI5" t="n">
-        <v>23160000</v>
+        <v>16761000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>62652000</v>
+        <v>54682000</v>
       </c>
       <c r="AK5" t="n">
-        <v>788449000</v>
+        <v>616021000</v>
       </c>
       <c r="AL5" t="n">
-        <v>180921000</v>
+        <v>230591000</v>
       </c>
       <c r="AM5" t="n">
-        <v>24400000</v>
+        <v>16268000</v>
       </c>
       <c r="AN5" t="n">
-        <v>545000</v>
+        <v>400000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3921000</v>
+        <v>11203000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3921000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>11203000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" t="n">
-        <v>31882000</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>31882000</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>16000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2166000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>24400000</v>
-      </c>
+        <v>20552000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>2166000</v>
+        <v>20552000</v>
       </c>
       <c r="AX5" t="n">
-        <v>114801000</v>
+        <v>111602000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-223589000</v>
+        <v>-218240000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>338390000</v>
+        <v>329842000</v>
       </c>
       <c r="BA5" t="n">
-        <v>820000</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>27535000</v>
+        <v>37324000</v>
       </c>
       <c r="BC5" t="n">
-        <v>205825000</v>
+        <v>185415000</v>
       </c>
       <c r="BD5" t="n">
-        <v>100302000</v>
+        <v>60766000</v>
       </c>
       <c r="BE5" t="n">
-        <v>3908000</v>
+        <v>46337000</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>607528000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>205053000</v>
-      </c>
+        <v>385430000</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>-24400000</v>
+        <v>168948000</v>
       </c>
       <c r="BK5" t="n">
-        <v>63987000</v>
+        <v>30673000</v>
       </c>
       <c r="BL5" t="n">
-        <v>39438000</v>
+        <v>22015000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10297000</v>
+        <v>3971000</v>
       </c>
       <c r="BN5" t="n">
-        <v>14252000</v>
+        <v>4687000</v>
       </c>
       <c r="BO5" t="n">
-        <v>35871000</v>
+        <v>120266000</v>
       </c>
       <c r="BP5" t="n">
-        <v>243014000</v>
+        <v>53619000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-5715000</v>
+        <v>-5991000</v>
       </c>
       <c r="BR5" t="n">
-        <v>103693000</v>
+        <v>59610000</v>
       </c>
       <c r="BS5" t="n">
-        <v>59603000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>24000</v>
-      </c>
+        <v>11924000</v>
+      </c>
+      <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="n">
-        <v>59579000</v>
+        <v>11924000</v>
       </c>
       <c r="BV5" t="n">
-        <v>59579000</v>
+        <v>11924000</v>
+      </c>
+      <c r="BW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>172006700</v>
+      </c>
+      <c r="C6" t="n">
+        <v>172006700</v>
+      </c>
+      <c r="D6" t="n">
+        <v>219340000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>256854000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-19778000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-210561000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-19778000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13628000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>774000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>774000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>476000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-298000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>774000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6537000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6739000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1138548000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>769532000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>172007000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>172007000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>697313000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8480000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1549000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1844000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5087000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5087000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>688833000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>251767000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8541000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>243226000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>253079000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>175701000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>17605000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>59773000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>697789000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>219517000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9660000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>387000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>15300000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20552000</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>20552000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>108098000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-226600000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>334698000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>38326000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>193235000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>56692000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>46445000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>478272000</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>241391000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>34597000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>23974000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5802000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4803000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>133089000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>45309000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-6346000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>51655000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>23886000</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="n">
+        <v>23886000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>23886000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
@@ -2490,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2727,538 +2881,605 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-29381000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-41206000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>67159000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11924000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28024000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6315000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-22415000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3408000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6777000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-8340000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>25953000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25953000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-41206000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>67159000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-8805000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>65000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-10601000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>-10601000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-1957000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>230000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2187000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>23143000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>35506000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-12363000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-17018000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2910000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-22904000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-24089000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2408000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-1223000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>13040000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>28783000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>28783000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5430000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-15570000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6142000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-52325000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>60229000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>60229000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>60229000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>110746000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>110746000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-6229000</v>
+        <v>-11374000</v>
       </c>
       <c r="C3" t="n">
-        <v>-75524000</v>
+        <v>-8217000</v>
       </c>
       <c r="D3" t="n">
-        <v>77336000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>22608000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-5136000</v>
+        <v>-5353000</v>
       </c>
       <c r="G3" t="n">
-        <v>28024000</v>
+        <v>24005000</v>
       </c>
       <c r="H3" t="n">
-        <v>24005000</v>
+        <v>59579000</v>
       </c>
       <c r="I3" t="n">
-        <v>3176000</v>
+        <v>8855000</v>
       </c>
       <c r="J3" t="n">
-        <v>843000</v>
+        <v>-44429000</v>
       </c>
       <c r="K3" t="n">
-        <v>-29531000</v>
+        <v>-29788000</v>
       </c>
       <c r="L3" t="n">
-        <v>318000</v>
+        <v>596000</v>
       </c>
       <c r="M3" t="n">
-        <v>-18239000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-28448000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>1812000</v>
+        <v>14391000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1812000</v>
+        <v>14391000</v>
       </c>
       <c r="R3" t="n">
-        <v>-75524000</v>
+        <v>-8217000</v>
       </c>
       <c r="S3" t="n">
-        <v>77336000</v>
+        <v>22608000</v>
       </c>
       <c r="T3" t="n">
-        <v>31467000</v>
+        <v>-8620000</v>
       </c>
       <c r="U3" t="n">
-        <v>69000</v>
+        <v>79000</v>
       </c>
       <c r="V3" t="n">
-        <v>194000</v>
+        <v>198000</v>
       </c>
       <c r="W3" t="n">
-        <v>-495000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-495000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-12750000</v>
+        <v>-80000</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-12750000</v>
+        <v>-80000</v>
       </c>
       <c r="AE3" t="n">
-        <v>62329000</v>
+        <v>37282000</v>
       </c>
       <c r="AF3" t="n">
-        <v>67465000</v>
+        <v>42635000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5136000</v>
+        <v>-5353000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1093000</v>
+        <v>-6021000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2300000</v>
+        <v>177000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>54992000</v>
+        <v>28949000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-52856000</v>
+        <v>-50486000</v>
       </c>
       <c r="AL3" t="n">
-        <v>22325000</v>
+        <v>4764000</v>
       </c>
       <c r="AM3" t="n">
-        <v>85523000</v>
+        <v>74671000</v>
       </c>
       <c r="AN3" t="n">
-        <v>23907000</v>
+        <v>22852000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AP3" t="n">
-        <v>29636000</v>
+        <v>31562000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>29636000</v>
+        <v>31562000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-194000</v>
+        <v>-8974000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-29606000</v>
+        <v>-12146000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2726000</v>
+        <v>6487000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-84601000</v>
+        <v>-96811000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-11374000</v>
+        <v>-6229000</v>
       </c>
       <c r="C4" t="n">
-        <v>-8217000</v>
+        <v>-75524000</v>
       </c>
       <c r="D4" t="n">
-        <v>22608000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>77336000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-5353000</v>
+        <v>-5136000</v>
       </c>
       <c r="G4" t="n">
+        <v>28024000</v>
+      </c>
+      <c r="H4" t="n">
         <v>24005000</v>
       </c>
-      <c r="H4" t="n">
-        <v>59579000</v>
-      </c>
       <c r="I4" t="n">
-        <v>8855000</v>
+        <v>3176000</v>
       </c>
       <c r="J4" t="n">
-        <v>-44429000</v>
+        <v>843000</v>
       </c>
       <c r="K4" t="n">
-        <v>-29788000</v>
+        <v>-29531000</v>
       </c>
       <c r="L4" t="n">
-        <v>596000</v>
+        <v>318000</v>
       </c>
       <c r="M4" t="n">
-        <v>-28448000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-18239000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>14391000</v>
+        <v>1812000</v>
       </c>
       <c r="Q4" t="n">
-        <v>14391000</v>
+        <v>1812000</v>
       </c>
       <c r="R4" t="n">
-        <v>-8217000</v>
+        <v>-75524000</v>
       </c>
       <c r="S4" t="n">
-        <v>22608000</v>
+        <v>77336000</v>
       </c>
       <c r="T4" t="n">
-        <v>-8620000</v>
+        <v>31467000</v>
       </c>
       <c r="U4" t="n">
-        <v>79000</v>
+        <v>69000</v>
       </c>
       <c r="V4" t="n">
-        <v>198000</v>
+        <v>194000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-495000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>-495000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-80000</v>
+        <v>-12750000</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-80000</v>
+        <v>-12750000</v>
       </c>
       <c r="AE4" t="n">
-        <v>37282000</v>
+        <v>62329000</v>
       </c>
       <c r="AF4" t="n">
-        <v>42635000</v>
+        <v>67465000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5353000</v>
+        <v>-5136000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6021000</v>
+        <v>-1093000</v>
       </c>
       <c r="AI4" t="n">
-        <v>177000</v>
+        <v>-2300000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28949000</v>
+        <v>54992000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-50486000</v>
+        <v>-52856000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4764000</v>
+        <v>22325000</v>
       </c>
       <c r="AM4" t="n">
-        <v>74671000</v>
+        <v>85523000</v>
       </c>
       <c r="AN4" t="n">
-        <v>22852000</v>
+        <v>23907000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>31562000</v>
+        <v>29636000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>31562000</v>
+        <v>29636000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-8974000</v>
+        <v>-194000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-12146000</v>
+        <v>-29606000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6487000</v>
+        <v>2726000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-96811000</v>
+        <v>-84601000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-85921000</v>
+        <v>-29381000</v>
       </c>
       <c r="C5" t="n">
-        <v>-286054000</v>
+        <v>-41206000</v>
       </c>
       <c r="D5" t="n">
-        <v>240658000</v>
+        <v>67159000</v>
       </c>
       <c r="E5" t="n">
-        <v>60229000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-10431000</v>
+        <v>-12363000</v>
       </c>
       <c r="G5" t="n">
-        <v>59579000</v>
+        <v>11924000</v>
       </c>
       <c r="H5" t="n">
-        <v>31774000</v>
+        <v>28024000</v>
       </c>
       <c r="I5" t="n">
-        <v>-7392000</v>
+        <v>6315000</v>
       </c>
       <c r="J5" t="n">
-        <v>35197000</v>
+        <v>-22415000</v>
       </c>
       <c r="K5" t="n">
-        <v>-19774000</v>
+        <v>3408000</v>
       </c>
       <c r="L5" t="n">
-        <v>37000</v>
+        <v>6777000</v>
       </c>
       <c r="M5" t="n">
-        <v>-21344000</v>
+        <v>-8340000</v>
       </c>
       <c r="N5" t="n">
-        <v>60229000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>60229000</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-45396000</v>
+        <v>25953000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-45396000</v>
+        <v>25953000</v>
       </c>
       <c r="R5" t="n">
-        <v>-286054000</v>
+        <v>-41206000</v>
       </c>
       <c r="S5" t="n">
-        <v>240658000</v>
+        <v>67159000</v>
       </c>
       <c r="T5" t="n">
-        <v>130461000</v>
+        <v>-8805000</v>
       </c>
       <c r="U5" t="n">
-        <v>118000</v>
+        <v>50000</v>
       </c>
       <c r="V5" t="n">
-        <v>134000</v>
+        <v>65000</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>110746000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>110746000</v>
-      </c>
+        <v>-10601000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-10601000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-8268000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>-1957000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>230000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>-8268000</v>
+        <v>-2187000</v>
       </c>
       <c r="AE5" t="n">
-        <v>27731000</v>
+        <v>23143000</v>
       </c>
       <c r="AF5" t="n">
-        <v>38162000</v>
+        <v>35506000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-10431000</v>
+        <v>-12363000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-75490000</v>
+        <v>-17018000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-16665000</v>
+        <v>-2910000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-655000</v>
+        <v>-22904000</v>
       </c>
       <c r="AK5" t="n">
-        <v>60947000</v>
+        <v>-24089000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-28568000</v>
+        <v>2408000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-33034000</v>
+        <v>-1223000</v>
       </c>
       <c r="AN5" t="n">
-        <v>22297000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
+        <v>13040000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>32537000</v>
+        <v>28783000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>32537000</v>
+        <v>28783000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-31571000</v>
+        <v>5430000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7330000</v>
+        <v>-15570000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-5050000</v>
+        <v>6142000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-92793000</v>
+        <v>-52325000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-27402000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-47366000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63591000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46392000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-6963000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23886000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11924000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-5005000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16967000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44640000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1314000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-6985000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46392000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>46392000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16225000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16225000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-47366000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>63591000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-7234000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>89000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-473000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-473000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-4283000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2680000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-6963000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-20439000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-228000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-3666000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>60002000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-2299000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-61369000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20069000</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>16416000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16416000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>611000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1499000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-72531000</v>
       </c>
     </row>
   </sheetData>
@@ -3272,7 +3493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL2"/>
+  <dimension ref="A1:EH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,690 +3519,670 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>website</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>industryKey</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>industryKey</t>
+          <t>industryDisp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>industryDisp</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sectorKey</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>sectorKey</t>
+          <t>sectorDisp</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>sectorDisp</t>
+          <t>longBusinessSummary</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>longBusinessSummary</t>
+          <t>fullTimeEmployees</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>fullTimeEmployees</t>
+          <t>companyOfficers</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>companyOfficers</t>
+          <t>compensationAsOfEpochDate</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>compensationAsOfEpochDate</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>open</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>fiveYearAvgDividendYield</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>pegRatio</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>pegRatio</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchangeTimezoneName</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>exchangeTimezoneShortName</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
       <c r="EH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4010,484 +4211,470 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>852 2851 1038</t>
+          <t>https://www.tayanggroup.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.tayanggroup.com</t>
+          <t>Advertising Agencies</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>advertising-agencies</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Advertising Agencies</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>advertising-agencies</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Advertising Agencies</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>communication-services</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>communication-services</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Ta Yang Group Holdings Limited, an investment holding company, designs, manufactures, and sells silicone rubber and related products in the People's Republic of China, Europe, and Hong Kong. It operates through Silicone Rubber and Related Products, Retail Services, Healthcare and Hotel Services, and Online Marketing Solution Services segments. The company's silicone rubber products is primarily used in consumer electronics, computer keyboards, mobile phone parts, automotive peripheral products, and customer-oriented consumer goods. It also provides retail, online marketing solution, healthcare and hotel, management, and retail services; and trades in silicone rubber. Ta Yang Group Holdings Limited was founded in 1991 and is based in Central, Hong Kong. Ta Yang Group Holdings Limited is a subsidiary of Lyton Maison Limited.</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>694</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Qi  Shi', 'age': 46, 'title': 'Executive Chairlady', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 3600000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiuhua  Li', 'age': 61, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 1480000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Terence  Wong', 'title': 'Financial Controller', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kai Kei  Lam', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1735603200</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+          <t>Ta Yang Group Holdings Limited, an investment holding company, designs, manufactures, and sells silicone rubber and related products in the People's Republic of China, the United Kingdom, and Hong Kong. It operates through Silicone Rubber and Related Products, Retail Services, Healthcare and Hotel Services, and Online Marketing Solution Services segments. It is involved in designing and production of medical device components, precision electronic product components, high-quality silicone parts, and other consumer electron. The company also provides retail, online marketing solutions, healthcare and hotel, management, and retail services; and trades in silicone rubber. Its silicone rubber products is primarily used in consumer electronics, computer keyboards, mobile phone parts, automotive peripheral products, and customer-oriented consumer goods. Ta Yang Group Holdings Limited was founded in 1991 and is based in Central, Hong Kong. Ta Yang Group Holdings Limited is a subsidiary of Lyton Maison Limited.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>633</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{'maxAge': 1, 'name': 'Ms. Qi  Shi', 'age': 46, 'title': 'Executive Chairlady', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 3600000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiuhua  Li', 'age': 61, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1440000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Terence  Wong', 'title': 'Financial Controller', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kai Kei  Lam', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="Q2" t="n">
+        <v>86400</v>
+      </c>
       <c r="R2" t="n">
-        <v>86400</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0.58</v>
       </c>
       <c r="T2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="W2" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="X2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="AB2" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>291858</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>270050</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>270050</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>96323752</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>96323752</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>36.86665</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.12705053</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.8759749999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>313043968</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.09674000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>172006700</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.70849997</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>172006700</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-73345000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1:10</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>1748390400</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-8.227</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.28205127</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BS2" t="n">
         <v>1354838400</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>160200</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>160200</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>327573</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>569080</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>569080</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110084288</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>108364221</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>36.86665</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.14744195</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.5769</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.929025</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BW2" t="n">
+        <v>44996000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-38051000</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>256854000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>758153024</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>53960.926</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>5.137</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>-4.70776</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>88453000</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>-15929250</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-20439000</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.11667</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-0.05019</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>-0.10516</v>
+      </c>
+      <c r="CO2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>329664096</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.076230004</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>172006700</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.70849997</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>172006700</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.353741</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1735603200</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1751241600</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-56915000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>1:10</t>
-        </is>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1748390400</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>22.759</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.032786846</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1354838400</v>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CA2" t="n">
-        <v>7304000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>14485000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>240248992</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>746627968</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>694.341</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>5.448</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.00601</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-0.51026</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>141260992</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-28713124</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>9475000</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>-0.435</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.1892</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.01932</v>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>1991.HK</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>1991.HK</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CU2" t="b">
+        <v>0</v>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
+          <t>finmb_32777778</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HKT</t>
         </is>
       </c>
       <c r="DA2" t="n">
-        <v>1.5873001</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DC2" t="inlineStr">
+        <v>28800000</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-3.4482725</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>1780453198</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.06309998</v>
-      </c>
       <c r="DG2" t="n">
-        <v>0.109377675</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.289025</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.31110573</v>
-      </c>
-      <c r="DJ2" t="n">
+        <v>1781764162</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>TA YANG GROUP</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Ta Yang Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.031799972</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.053734325</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.315975</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.36071235</v>
+      </c>
+      <c r="DP2" t="n">
         <v>15</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DQ2" t="n">
         <v>15</v>
       </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
         <v>1181266200000</v>
       </c>
-      <c r="DO2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>0.6 - 0.68</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DU2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>0.56 - 0.62</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DR2" t="n">
-        <v>327573</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.21499997</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.50588226</v>
-      </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DX2" t="n">
+        <v>291858</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.13499999</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.31764704</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>0.425 - 1.8</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.64444447</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>3.2786846</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="EB2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.6888889</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-28.205126</v>
+      </c>
+      <c r="EE2" t="n">
         <v>1743169130</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EF2" t="n">
         <v>1743169130</v>
       </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>finmb_32777778</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>TA YANG GROUP</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Ta Yang Group Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr"/>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
